--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -94,7 +94,10 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -103,19 +106,10 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
   </si>
   <si>
     <t>JUAN</t>
@@ -124,7 +118,10 @@
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>QUERO</t>
@@ -133,19 +130,7 @@
     <t>FIERROS</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>PULIDO</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
@@ -154,7 +139,10 @@
     <t>JOHANAN</t>
   </si>
   <si>
-    <t>ADBIEL</t>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DIEGO JESUS</t>
@@ -163,19 +151,10 @@
     <t>ALDO EMANUEL</t>
   </si>
   <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALDAIR</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -605,16 +584,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>82.93000000000001</v>
+        <v>85.37</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -823,16 +802,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -846,16 +828,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -869,16 +854,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -892,16 +880,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -915,16 +906,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -938,16 +932,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H7">
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -961,16 +958,19 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H8">
+        <v>7.6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -984,16 +984,19 @@
         <v>28</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H9">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1049,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1084,7 +1087,7 @@
         <v>82.93000000000001</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1110,7 +1113,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1127,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>89.29000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1153,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>77.42</v>
+        <v>96.77</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1179,16 +1182,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>64.52</v>
+        <v>93.55</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1205,16 +1208,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>77.42</v>
+        <v>93.55</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1231,16 +1234,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H9">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1250,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1288,10 +1291,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1311,10 +1314,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1328,22 +1331,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920084</v>
+        <v>24330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1351,19 +1354,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>22330051920003</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -1374,22 +1377,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>22330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1397,22 +1400,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920033</v>
+        <v>22330051920231</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1420,19 +1423,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920051</v>
+        <v>22330051920189</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1443,70 +1446,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920002</v>
+        <v>22330051920401</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920034</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920036</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -91,67 +91,67 @@
     <t>ESCOBAR</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
     <t>PULIDO</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
   </si>
   <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
     <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920141</v>
+        <v>24330051920026</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920026</v>
+        <v>22330051920003</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -1343,10 +1343,10 @@
         <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920003</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920015</v>
+        <v>22330051920231</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1389,10 +1389,10 @@
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1400,13 +1400,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920231</v>
+        <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -1415,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1423,25 +1423,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920189</v>
+        <v>24330051920141</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -103,15 +103,15 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
     <t>JUAN</t>
   </si>
   <si>
@@ -148,13 +148,13 @@
     <t>ALDO EMANUEL</t>
   </si>
   <si>
+    <t>JOHANAN</t>
+  </si>
+  <si>
+    <t>JUAN EMANUEL</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -1400,45 +1400,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920189</v>
+        <v>24330051920141</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920141</v>
+        <v>22330051920401</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1446,13 +1446,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920401</v>
+        <v>22330051920189</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>1</v>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,33 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
@@ -100,9 +127,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -112,12 +136,36 @@
     <t>JENKINS</t>
   </si>
   <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>JUAN</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -131,6 +179,27 @@
   </si>
   <si>
     <t>PULIDO</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>ELIAN RAMON</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
@@ -1253,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1285,16 +1354,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920103</v>
+        <v>24330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1303,21 +1372,21 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920026</v>
+        <v>24330051920326</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1326,113 +1395,113 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920003</v>
+        <v>24330051920233</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920015</v>
+        <v>24330051920332</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>24330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920141</v>
+        <v>24330051920335</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920401</v>
+        <v>21330051420317</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1441,21 +1510,21 @@
         <v>16</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1464,6 +1533,259 @@
         <v>15</v>
       </c>
       <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920031</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920191</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920191</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920003</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920231</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920141</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920401</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920189</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -91,10 +91,31 @@
     <t>CID</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>ARELLANO</t>
+    <t>RAZCON</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -106,30 +127,21 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>ESCOBAR</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
@@ -139,10 +151,28 @@
     <t>OROZCO</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>PAZ</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>CHICUELLAR</t>
@@ -154,27 +184,15 @@
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
     <t>ADRIAN</t>
   </si>
   <si>
@@ -184,6 +202,30 @@
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>MARCO DIDIEL</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
     <t>ELIAN RAMON</t>
   </si>
   <si>
@@ -193,31 +235,19 @@
     <t>JAVIER</t>
   </si>
   <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
   </si>
   <si>
+    <t>JOHANAN</t>
+  </si>
+  <si>
     <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
@@ -673,10 +703,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -685,7 +715,7 @@
         <v>25</v>
       </c>
       <c r="G4">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H4">
         <v>7.9</v>
@@ -699,7 +729,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -708,13 +738,13 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>89.29000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -920,10 +950,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -932,7 +962,7 @@
         <v>25</v>
       </c>
       <c r="G4">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H4">
         <v>7.9</v>
@@ -946,7 +976,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -955,13 +985,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1167,10 +1197,10 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1179,7 +1209,7 @@
         <v>25</v>
       </c>
       <c r="G4">
-        <v>89.29000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H4">
         <v>8.300000000000001</v>
@@ -1193,7 +1223,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1202,13 +1232,13 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1322,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1360,10 +1390,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1377,16 +1407,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1400,16 +1430,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920233</v>
+        <v>24330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1418,21 +1448,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920332</v>
+        <v>24330051920404</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1441,50 +1471,50 @@
         <v>13</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920065</v>
+        <v>21330051420317</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920335</v>
+        <v>24330051920233</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1492,22 +1522,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051420317</v>
+        <v>24330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -1515,22 +1545,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920031</v>
+        <v>24330051920307</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1538,22 +1568,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920031</v>
+        <v>22330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1561,19 +1591,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920191</v>
+        <v>22330051920031</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -1584,16 +1614,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920191</v>
+        <v>22330051920031</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1607,68 +1637,68 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920103</v>
+        <v>22330051920191</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920026</v>
+        <v>22330051920191</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920003</v>
+        <v>24330051920332</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1676,22 +1706,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920015</v>
+        <v>24330051920065</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1699,22 +1729,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920231</v>
+        <v>24330051920335</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1722,70 +1752,162 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920141</v>
+        <v>22330051920003</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920401</v>
+        <v>22330051920015</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920189</v>
+        <v>24330051920103</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920026</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920401</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
         <v>10</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920189</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
         <v>15</v>
       </c>
-      <c r="G20">
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
   <si>
     <t>Mat</t>
   </si>
@@ -88,136 +88,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>CID</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>RAZCON</t>
+  </si>
+  <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>RAZCON</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
   </si>
   <si>
     <t>OROZCO</t>
   </si>
   <si>
-    <t>RANGEL</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CHICUELLAR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>ANGEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>AXEL BENITO</t>
-  </si>
-  <si>
-    <t>YERIEL</t>
+    <t>JOSE ARTURO</t>
   </si>
   <si>
     <t>MARCO DIDIEL</t>
-  </si>
-  <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
   </si>
   <si>
     <t>RICARDO</t>
@@ -1352,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1384,16 +1375,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1407,22 +1398,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920329</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1430,22 +1421,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920145</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1453,62 +1444,62 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920404</v>
+        <v>24330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051420317</v>
+        <v>24330051920328</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920233</v>
+        <v>24330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1522,16 +1513,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920326</v>
+        <v>24330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1545,22 +1536,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920307</v>
+        <v>24330051920404</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>3</v>
@@ -1568,22 +1559,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920231</v>
+        <v>22330051920031</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1594,16 +1585,16 @@
         <v>22330051920031</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -1614,19 +1605,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920031</v>
+        <v>22330051920191</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
@@ -1640,16 +1631,16 @@
         <v>22330051920191</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1660,39 +1651,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920191</v>
+        <v>24330051920332</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920332</v>
+        <v>24330051920065</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1706,16 +1697,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920065</v>
+        <v>24330051920335</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1729,22 +1720,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920335</v>
+        <v>22330051920003</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1752,16 +1743,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920003</v>
+        <v>22330051920015</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1775,39 +1766,39 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920015</v>
+        <v>24330051920103</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920103</v>
+        <v>24330051920141</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1821,16 +1812,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920141</v>
+        <v>24330051920026</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1844,22 +1835,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920026</v>
+        <v>22330051920401</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1867,47 +1858,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920401</v>
+        <v>22330051920189</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920189</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -91,160 +91,19 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>RAZCON</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CHICUELLAR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JUAN</t>
+    <t>YERIEL</t>
   </si>
   <si>
     <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>YERIEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANGEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>MARCO DIDIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ELIAN RAMON</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>GIOVANNI ARIEL</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
 </sst>
 </file>
@@ -697,19 +556,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>86.20999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -944,19 +803,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>86.20999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1142,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>92.5</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1168,13 +1027,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>82.93000000000001</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -1191,19 +1050,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1220,16 +1079,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1246,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1272,16 +1131,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1298,16 +1157,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1324,16 +1183,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9">
-        <v>85.70999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1381,10 +1240,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1398,484 +1257,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920010</v>
+        <v>24330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920010</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920233</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920328</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920326</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920307</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920404</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920031</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920031</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920191</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920191</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920332</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920065</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920335</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920003</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920015</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920103</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920141</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920026</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920401</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920189</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23">
         <v>1</v>
       </c>
     </row>
